--- a/timetable_generator/timetable_outputs/DSAI_Sem5_SectionA_Timetable.xlsx
+++ b/timetable_generator/timetable_outputs/DSAI_Sem5_SectionA_Timetable.xlsx
@@ -468,30 +468,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>DS303
+Algorithms and Artificial Intelligence
+C101
+Dr.Animesh Chaturvedi
+[COMMON]</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>DS302
 Computer Communication Networks
 C101
-Dr.Shirshendu Layek</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>DS303
-Algorithms and Artificial Intelligence
-C101
-Dr.Animesh Chaturvedi</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>DS302
-Computer Communication Networks
-C101
-Dr.Shirshendu Layek</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
+Dr.Shirshendu Layek
+[COMMON]
+[TUTORIAL]</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -501,13 +497,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>CS307
+Machine Learning
+C101
+Dr.Siddharth
+[COMMON]</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>DS303
 Algorithms and Artificial Intelligence
 C101
-Dr.Animesh Chaturvedi</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+Dr.Animesh Chaturvedi
+[COMMON]</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
@@ -518,32 +523,28 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>DS302
-Computer Communication Networks
-C101
-Dr.Shirshendu Layek</t>
-        </is>
-      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DS303
+Algorithms and Artificial Intelligence
+C101
+Dr.Animesh Chaturvedi
+[COMMON]
+[TUTORIAL]</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>CS307
 Machine Learning
 C101
-Dr.Siddharth</t>
+Dr.Siddharth
+[COMMON]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>CS307
-Machine Learning
-C101
-Dr.Siddharth</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -555,21 +556,23 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>DS303
-Algorithms and Artificial Intelligence
-C101
-Dr.Animesh Chaturvedi</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
           <t>DS302
 Computer Communication Networks
 C101
-Dr.Shirshendu Layek</t>
-        </is>
-      </c>
+Dr.Shirshendu Layek
+[COMMON]</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>DS302
+Computer Communication Networks
+C101
+Dr.Shirshendu Layek
+[COMMON]</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -582,12 +585,21 @@
           <t>CS307
 Machine Learning
 C101
-Dr.Siddharth</t>
+Dr.Siddharth
+[COMMON]</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>DS302
+Computer Communication Networks
+C101
+Dr.Shirshendu Layek
+[COMMON]</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
     </row>
   </sheetData>
